--- a/analisi/basiano-manzoni-fix-and-flip.xlsx
+++ b/analisi/basiano-manzoni-fix-and-flip.xlsx
@@ -59,8 +59,8 @@
     <definedName name="Arv">'Inputs'!$B$52</definedName>
     <definedName name="LavoriTot">'Inputs'!$B$53</definedName>
     <definedName name="TassoMese">'Inputs'!$B$54</definedName>
-    <definedName name="ErroriTot">'Checks'!$B$22</definedName>
-    <definedName name="AvvisiTot">'Checks'!$B$23</definedName>
+    <definedName name="ErroriTot">'Checks'!$B$23</definedName>
+    <definedName name="AvvisiTot">'Checks'!$B$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Via Alessandro Manzoni 7, Basiano (MI), zona OMI B1. Alloggio A/3 su tre livelli (terra, primo, sottotetto non abitabile) in cascina del 1790. RGE 168/2025, IV esperimento, asta 02/12/2026.</t>
+          <t>Via Alessandro Manzoni 7, Basiano (MI), zona OMI B1. Alloggio A/3 su tre livelli (terra, primo, sottotetto non abitabile) in cascina del 1790. RGE 168/2025, probabile IV esperimento (allegato PVP '4 AVVISO DI VENDITA', base al 52% della perizia), asta 02/12/2026.</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Storico QRE: 19 aste 2022-2026, mediana 1,20 (radar); al IV esperimento con base al 52% della perizia la gara puo' salire di piu'</t>
+          <t>Storico QRE: 19 aste 2022-2026, mediana 1,20 (radar); con la base al 52% della perizia la gara puo' salire di piu'</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>IPOTESI: copertura e facciate in pessimo stato (perizia), nessun condominio che le ripartisca</t>
+          <t>IPOTESI: copertura e facciate in pessimo stato (perizia), nessun condominio che le ripartisca, edificio di interesse storico-culturale nel PGT</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -7321,7 +7321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sottotetto senza permanenza di persone: non vendibile come camera</t>
+          <t>PGT: cascina di impianto storico, edificio di interesse storico-culturale: titoli e materiali vincolati per copertura e facciate</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
@@ -7331,7 +7331,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Occupato dall'esecutato: tempi di liberazione incerti</t>
+          <t>Sottotetto senza permanenza di persone: non vendibile come camera</t>
         </is>
       </c>
       <c r="B18" s="14" t="n">
@@ -7341,7 +7341,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Il radar riporta 0 aste deserte, l'avviso e' il IV esperimento (difetto noto: dettaglio non aperto sotto 100 mila)</t>
+          <t>Occupato dall'esecutato: tempi di liberazione incerti</t>
         </is>
       </c>
       <c r="B19" s="14" t="n">
@@ -7351,32 +7351,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aliquota di registro e trattamento IVA da confermare col parere fiscale</t>
+          <t>Il radar riporta 0 aste deserte, l'allegato PVP e' il '4 AVVISO DI VENDITA' (dettaglio non aperto sotto 100 mila)</t>
         </is>
       </c>
       <c r="B20" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Errori totali</t>
-        </is>
-      </c>
-      <c r="B22" s="7">
-        <f>SUM(B3:B10)</f>
-        <v/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Aliquota di registro e trattamento IVA da confermare col parere fiscale</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>Errori totali</t>
+        </is>
+      </c>
+      <c r="B23" s="7">
+        <f>SUM(B3:B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>Avvisi totali</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(B13:B20)</f>
+      <c r="B24" s="7">
+        <f>SUM(B13:B21)</f>
         <v/>
       </c>
     </row>
